--- a/su25fungv2.xlsx
+++ b/su25fungv2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mario\OneDrive\Documents\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44887989-514F-4BB8-81D2-797AAEC962C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C5C6D4-2661-4B3C-B7CC-93C60AFC0EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{B92E0137-6717-430D-BC87-94BB95C29D48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B92E0137-6717-430D-BC87-94BB95C29D48}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="7">
   <si>
     <t>Treatment</t>
   </si>
@@ -47,49 +47,16 @@
     <t>Treatment_sum</t>
   </si>
   <si>
-    <t>Control_NB</t>
-  </si>
-  <si>
-    <t>Week 1</t>
+    <t>C_NB</t>
   </si>
   <si>
     <t>MP_NB</t>
   </si>
   <si>
-    <t>Control_B</t>
+    <t>C_B</t>
   </si>
   <si>
     <t>MP_B</t>
-  </si>
-  <si>
-    <t>Week 2</t>
-  </si>
-  <si>
-    <t>Week 3</t>
-  </si>
-  <si>
-    <t>Week 4</t>
-  </si>
-  <si>
-    <t>Week 5</t>
-  </si>
-  <si>
-    <t>Week 6</t>
-  </si>
-  <si>
-    <t>Week 7</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
-    <t>Week 9</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Week 11</t>
   </si>
 </sst>
 </file>
@@ -479,8 +446,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -488,21 +455,15 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -510,10 +471,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -523,8 +481,8 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -532,21 +490,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -554,10 +506,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -567,8 +516,8 @@
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -576,10 +525,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -587,10 +533,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -598,10 +541,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -611,8 +551,8 @@
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
+      <c r="B14">
+        <v>4</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -620,10 +560,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>9</v>
@@ -631,10 +568,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -642,10 +576,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -655,8 +586,8 @@
       <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="B18" t="s">
-        <v>11</v>
+      <c r="B18">
+        <v>5</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -664,10 +595,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>13</v>
@@ -675,10 +603,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -686,10 +611,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -699,8 +621,8 @@
       <c r="A22" t="s">
         <v>3</v>
       </c>
-      <c r="B22" t="s">
-        <v>12</v>
+      <c r="B22">
+        <v>6</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -708,10 +630,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>17</v>
@@ -719,10 +638,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>8</v>
@@ -730,10 +646,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>8</v>
@@ -743,8 +656,8 @@
       <c r="A26" t="s">
         <v>3</v>
       </c>
-      <c r="B26" t="s">
-        <v>13</v>
+      <c r="B26">
+        <v>7</v>
       </c>
       <c r="C26">
         <v>16</v>
@@ -752,10 +665,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>18</v>
@@ -763,10 +673,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>8</v>
@@ -774,10 +681,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -787,8 +691,8 @@
       <c r="A30" t="s">
         <v>3</v>
       </c>
-      <c r="B30" t="s">
-        <v>14</v>
+      <c r="B30">
+        <v>8</v>
       </c>
       <c r="C30">
         <v>16</v>
@@ -796,10 +700,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>19</v>
@@ -807,10 +708,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -818,10 +716,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -831,8 +726,8 @@
       <c r="A34" t="s">
         <v>3</v>
       </c>
-      <c r="B34" t="s">
-        <v>15</v>
+      <c r="B34">
+        <v>9</v>
       </c>
       <c r="C34">
         <v>16</v>
@@ -840,10 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>19</v>
@@ -851,10 +743,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>8</v>
@@ -862,10 +751,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>8</v>
@@ -875,8 +761,8 @@
       <c r="A38" t="s">
         <v>3</v>
       </c>
-      <c r="B38" t="s">
-        <v>16</v>
+      <c r="B38">
+        <v>10</v>
       </c>
       <c r="C38">
         <v>16</v>
@@ -884,10 +770,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>19</v>
@@ -895,10 +778,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>8</v>
@@ -906,10 +786,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>8</v>
@@ -919,8 +796,8 @@
       <c r="A42" t="s">
         <v>3</v>
       </c>
-      <c r="B42" t="s">
-        <v>17</v>
+      <c r="B42">
+        <v>11</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -928,10 +805,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>19</v>
@@ -939,10 +813,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>8</v>
@@ -950,10 +821,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C45">
         <v>8</v>
